--- a/survey_templates/050_podcast_listener_survey--survey_templates.xlsx
+++ b/survey_templates/050_podcast_listener_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1130,8 +1130,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'very_likely'}</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_likely'}</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'not_likely'}</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'news'}</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'news'}</t>
+          <t>news</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'stories'}</t>
+          <t>stories</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'stories'}</t>
+          <t>stories</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'interviews'}</t>
+          <t>interviews</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'interviews'}</t>
+          <t>interviews</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'video'}</t>
+          <t>video</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'written'}</t>
+          <t>written</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'written'}</t>
+          <t>written</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'mobile_phone'}</t>
+          <t>mobile phone</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'often'}</t>
+          <t>often</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'very_often'}</t>
+          <t>very often</t>
         </is>
       </c>
     </row>
